--- a/src/test/resources/test-data/Login.xlsx
+++ b/src/test/resources/test-data/Login.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sathy\work\SathyaWorkspace\dsAlgoProject\src\test\resources\Exceldata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prasaddige/git/DsAlgoTest/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D771D8-32FD-4140-B6D6-9D44097E80D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40D7E0C-8507-BF47-B827-F67E208DE748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="User_Credentials" sheetId="1" r:id="rId1"/>
     <sheet name="pythonCode" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>username</t>
   </si>
@@ -30,27 +30,6 @@
   </si>
   <si>
     <t>expectedmessage</t>
-  </si>
-  <si>
-    <t>Numpysdet84</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>Invalid Username and Password</t>
-  </si>
-  <si>
-    <t>sdet84batch</t>
-  </si>
-  <si>
-    <t>You are logged in</t>
-  </si>
-  <si>
-    <t>Numpysdet86</t>
-  </si>
-  <si>
-    <t>sdet86batch</t>
   </si>
   <si>
     <t>pythonCode</t>
@@ -141,17 +120,41 @@
     <t>[4, 9, 9, 49, 121]</t>
   </si>
   <si>
-    <t>Please check your user id</t>
-  </si>
-  <si>
-    <t>Please check your password</t>
+    <t>User4</t>
+  </si>
+  <si>
+    <t>Passsword3</t>
+  </si>
+  <si>
+    <t>Password4</t>
+  </si>
+  <si>
+    <t>Reason3</t>
+  </si>
+  <si>
+    <t>Reason4</t>
+  </si>
+  <si>
+    <t>ArinSwalke</t>
+  </si>
+  <si>
+    <t>Nandita@09</t>
+  </si>
+  <si>
+    <t>You are logged in</t>
+  </si>
+  <si>
+    <t>Nandita@00</t>
+  </si>
+  <si>
+    <t>Invalid Username and Password</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,12 +165,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -193,18 +206,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -419,15 +435,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="26" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,51 +454,53 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{724C5E09-173B-754F-AC57-82E92CEF5886}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{FA6909A9-428F-094C-A47A-0B3320CD0FA7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -494,97 +512,98 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="1" max="1" width="199.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="213.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/test-data/Login.xlsx
+++ b/src/test/resources/test-data/Login.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prasaddige/git/DsAlgoTest/src/test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prasaddige/git/DsAlgoTest/src/test/resources/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40D7E0C-8507-BF47-B827-F67E208DE748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D65C5E8-A6B0-804A-8A8E-3B630CF18DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User_Credentials" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>username</t>
   </si>
@@ -58,68 +58,6 @@
 search([12, 23, 45, 67, 6, 90] , 12)</t>
   </si>
   <si>
-    <t>Element Found</t>
-  </si>
-  <si>
-    <t>submission success</t>
-  </si>
-  <si>
-    <t>def findMaxConsecutiveOnes(nums) :
-count = 0
-result = 0
-for i in range(0, len(nums)):
-if (nums[i] == 0):
-count = 0
-\b
-\b
-else:
-count+= 1
-\b
-\b
-result = max(result, count)
-\b
-\b
-print(result)
-\b
-\b
-findMaxConsecutiveOnes([1,0,1,1,0,1])</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>def findNumbers(nums):
-c=0
-for i in nums:
-j=str(i)
-x=len(j)
-if x%2==0:
-c=c+1
-\b
-\b
-\b
-\b
-print c
-return c
-findNumbers([12,345,2,6,7896])</t>
-  </si>
-  <si>
-    <t>def sortedSquares(nums):
-squares_list = []
-for i in range(0, len(nums)):
-square = nums[i] * nums[i];
-squares_list.append(square)
-\b
-\b
-sorted_squares_list = sorted(squares_list)
-print sorted_squares_list;
-return sorted_squares_list;
-sortedSquares([-7,-3,2,3,11])</t>
-  </si>
-  <si>
-    <t>[4, 9, 9, 49, 121]</t>
-  </si>
-  <si>
     <t>User4</t>
   </si>
   <si>
@@ -148,13 +86,22 @@
   </si>
   <si>
     <t>Invalid Username and Password</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>NameError: name 'hello' is not defined on line 1</t>
+  </si>
+  <si>
+    <t>SyntaxError: bad input on line 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,12 +116,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -183,18 +124,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -208,16 +143,12 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -456,44 +387,44 @@
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -511,99 +442,49 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="199.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="213.83203125" customWidth="1"/>
+    <col min="1" max="1" width="115.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
+      <c r="B4" s="1"/>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
